--- a/data/trans_orig/P20-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34892</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28690</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31262</t>
+          <t>32020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56451</t>
+          <t>57121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438884</t>
+          <t>439729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458097</t>
+          <t>458229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277990</t>
+          <t>278849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294471</t>
+          <t>294911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724006</t>
+          <t>723336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749195</t>
+          <t>748437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>40552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58835</t>
+          <t>58820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341679</t>
+          <t>342283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358075</t>
+          <t>358168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329824</t>
+          <t>331313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351724</t>
+          <t>352394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679964</t>
+          <t>679979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706842</t>
+          <t>706060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26732</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51501</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511831</t>
+          <t>510607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529283</t>
+          <t>528721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141434</t>
+          <t>141206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157574</t>
+          <t>158349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658670</t>
+          <t>656363</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>683439</t>
+          <t>683757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72050</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48558</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79076</t>
+          <t>79060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101164</t>
+          <t>97654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141182</t>
+          <t>140621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1166284</t>
+          <t>1165586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1194730</t>
+          <t>1195485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635209</t>
+          <t>635225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>665727</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1811438</t>
+          <t>1811999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1851456</t>
+          <t>1854966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54545</t>
+          <t>56093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>71022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325961</t>
+          <t>326523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341103</t>
+          <t>341679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>514207</t>
+          <t>512659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539843</t>
+          <t>539417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>847498</t>
+          <t>848285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876659</t>
+          <t>877049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>65271</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99869</t>
+          <t>96849</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68197</t>
+          <t>67686</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104676</t>
+          <t>102047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286371</t>
+          <t>286284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296368</t>
+          <t>296370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1148891</t>
+          <t>1151911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1185281</t>
+          <t>1183489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1441340</t>
+          <t>1443969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1477819</t>
+          <t>1478330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114730</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160050</t>
+          <t>159715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221383</t>
+          <t>220282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283697</t>
+          <t>283130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349964</t>
+          <t>348385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425773</t>
+          <t>421616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3109196</t>
+          <t>3109531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3154516</t>
+          <t>3155093</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3094427</t>
+          <t>3094994</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3156741</t>
+          <t>3157842</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6221597</t>
+          <t>6225754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6297406</t>
+          <t>6298985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33108</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46934</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41408</t>
+          <t>41258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73356</t>
+          <t>72513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404103</t>
+          <t>403308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424085</t>
+          <t>424709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267520</t>
+          <t>265788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290434</t>
+          <t>290446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678309</t>
+          <t>679152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710257</t>
+          <t>710407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>46420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>35576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>65295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391214</t>
+          <t>391505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407954</t>
+          <t>408813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>292000</t>
+          <t>291591</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315272</t>
+          <t>314017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691615</t>
+          <t>691513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718907</t>
+          <t>721232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>37176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65043</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56008</t>
+          <t>57559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90231</t>
+          <t>90655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564372</t>
+          <t>564364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>593057</t>
+          <t>592239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227636</t>
+          <t>226497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245452</t>
+          <t>245663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799313</t>
+          <t>798889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833536</t>
+          <t>831985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58938</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92285</t>
+          <t>93021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99431</t>
+          <t>100463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132347</t>
+          <t>130800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180846</t>
+          <t>182425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1066724</t>
+          <t>1065988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1100071</t>
+          <t>1100377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667226</t>
+          <t>666194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702290</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1744821</t>
+          <t>1743242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1793320</t>
+          <t>1794867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64049</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98742</t>
+          <t>97547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96939</t>
+          <t>97394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139655</t>
+          <t>142826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459040</t>
+          <t>458231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484603</t>
+          <t>484262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662780</t>
+          <t>663975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697473</t>
+          <t>697793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1132463</t>
+          <t>1129292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1175179</t>
+          <t>1174724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69535</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103268</t>
+          <t>104384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76468</t>
+          <t>75221</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112899</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250849</t>
+          <t>250133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261045</t>
+          <t>260970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1006083</t>
+          <t>1004967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1039816</t>
+          <t>1040473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261287</t>
+          <t>1261715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1297718</t>
+          <t>1298965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178552</t>
+          <t>177766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234158</t>
+          <t>234085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>299847</t>
+          <t>303343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>374841</t>
+          <t>373186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>495234</t>
+          <t>499601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>590830</t>
+          <t>592751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3185704</t>
+          <t>3185777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3241310</t>
+          <t>3242096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3175284</t>
+          <t>3176939</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3250278</t>
+          <t>3246782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6379158</t>
+          <t>6377237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6474754</t>
+          <t>6470387</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>47453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45027</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>76229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391368</t>
+          <t>390815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412006</t>
+          <t>412163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300787</t>
+          <t>299602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>322930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698810</t>
+          <t>699918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731120</t>
+          <t>731206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30861</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47434</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71071</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346366</t>
+          <t>344378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364735</t>
+          <t>364641</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324839</t>
+          <t>325793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347653</t>
+          <t>348771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678429</t>
+          <t>679198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707641</t>
+          <t>709150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35753</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63597</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477494</t>
+          <t>477205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499534</t>
+          <t>499269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140314</t>
+          <t>140958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157420</t>
+          <t>157168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624439</t>
+          <t>625370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652283</t>
+          <t>653237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>39868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70323</t>
+          <t>69830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92833</t>
+          <t>96285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108806</t>
+          <t>111857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152489</t>
+          <t>155437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1079315</t>
+          <t>1079808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108345</t>
+          <t>1109770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733043</t>
+          <t>729591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>766218</t>
+          <t>764070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1823025</t>
+          <t>1820077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1866708</t>
+          <t>1863657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>33103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53444</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86232</t>
+          <t>87428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588588</t>
+          <t>587603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>607262</t>
+          <t>607494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675434</t>
+          <t>676696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703437</t>
+          <t>703821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1272718</t>
+          <t>1271522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1305506</t>
+          <t>1303831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50506</t>
+          <t>51244</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>84902</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58228</t>
+          <t>58578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96249</t>
+          <t>94318</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270790</t>
+          <t>270991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282444</t>
+          <t>282837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>996769</t>
+          <t>997123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1031519</t>
+          <t>1030781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1272921</t>
+          <t>1274852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1310942</t>
+          <t>1310592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138505</t>
+          <t>140190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188784</t>
+          <t>190791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>242521</t>
+          <t>241709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>306227</t>
+          <t>308340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>395495</t>
+          <t>393869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>480553</t>
+          <t>478221</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3196938</t>
+          <t>3194931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3247217</t>
+          <t>3245532</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3225369</t>
+          <t>3223256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3289075</t>
+          <t>3289887</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6436765</t>
+          <t>6439097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6521823</t>
+          <t>6523449</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>44047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80165</t>
+          <t>78135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>458870</t>
+          <t>461165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482707</t>
+          <t>482522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405900</t>
+          <t>405180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>425201</t>
+          <t>423976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>872514</t>
+          <t>874544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>902651</t>
+          <t>903933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>39602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38706</t>
+          <t>39558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63280</t>
+          <t>64804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>419801</t>
+          <t>421121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437711</t>
+          <t>438424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344114</t>
+          <t>342978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361929</t>
+          <t>361564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771513</t>
+          <t>769989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>796087</t>
+          <t>795235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55618</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72322</t>
+          <t>71733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612646</t>
+          <t>614549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656577</t>
+          <t>657521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141007</t>
+          <t>141316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156933</t>
+          <t>156611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>762853</t>
+          <t>763442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817552</t>
+          <t>815242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78029</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73005</t>
+          <t>71956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79380</t>
+          <t>80391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136065</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>956790</t>
+          <t>956800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>988708</t>
+          <t>988797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>905089</t>
+          <t>906138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950393</t>
+          <t>951124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1876847</t>
+          <t>1876181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1933532</t>
+          <t>1932521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29671</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>50647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55920</t>
+          <t>54206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>63893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99409</t>
+          <t>98923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422852</t>
+          <t>424399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>445375</t>
+          <t>445515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>783076</t>
+          <t>784790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809252</t>
+          <t>809742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1214632</t>
+          <t>1215118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1251496</t>
+          <t>1250148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>56087</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58007</t>
+          <t>57066</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231819</t>
+          <t>228064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239939</t>
+          <t>239816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>707695</t>
+          <t>705284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>730097</t>
+          <t>730015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943871</t>
+          <t>944812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968798</t>
+          <t>969219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144461</t>
+          <t>145822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217286</t>
+          <t>218520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169874</t>
+          <t>171054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239486</t>
+          <t>241519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343434</t>
+          <t>341985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446374</t>
+          <t>443982</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3158774</t>
+          <t>3157540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3231599</t>
+          <t>3230238</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3335932</t>
+          <t>3333899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3405544</t>
+          <t>3404364</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6505105</t>
+          <t>6507497</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6608045</t>
+          <t>6609494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15547</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11550</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>28609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32020</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>56831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439729</t>
+          <t>438982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458229</t>
+          <t>458939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278849</t>
+          <t>278071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294911</t>
+          <t>295130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723336</t>
+          <t>723626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>748437</t>
+          <t>748951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40552</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32739</t>
+          <t>33724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58820</t>
+          <t>58463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342283</t>
+          <t>342459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358168</t>
+          <t>358469</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331313</t>
+          <t>329909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352394</t>
+          <t>351783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679979</t>
+          <t>680336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>705075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510607</t>
+          <t>511431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528721</t>
+          <t>529012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141206</t>
+          <t>142730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158349</t>
+          <t>158390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656363</t>
+          <t>659119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>683757</t>
+          <t>683438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72748</t>
+          <t>73739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>49568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79060</t>
+          <t>79610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>101275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140621</t>
+          <t>142176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1165586</t>
+          <t>1164595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1195485</t>
+          <t>1195515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635225</t>
+          <t>634675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>664717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1811999</t>
+          <t>1810444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1854966</t>
+          <t>1851345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>55932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71022</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326523</t>
+          <t>326705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341679</t>
+          <t>342102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>512659</t>
+          <t>512820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539417</t>
+          <t>539670</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848285</t>
+          <t>847307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>877049</t>
+          <t>876732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65271</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96849</t>
+          <t>99693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67686</t>
+          <t>66991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102047</t>
+          <t>102750</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286284</t>
+          <t>286533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296370</t>
+          <t>296368</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1151911</t>
+          <t>1149067</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1183489</t>
+          <t>1183229</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1443969</t>
+          <t>1443266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1478330</t>
+          <t>1479025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159715</t>
+          <t>159036</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220282</t>
+          <t>218751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283130</t>
+          <t>280389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>348385</t>
+          <t>346364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>421616</t>
+          <t>420427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3109531</t>
+          <t>3110210</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3155093</t>
+          <t>3156194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3094994</t>
+          <t>3097735</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3157842</t>
+          <t>3159373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6225754</t>
+          <t>6226943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6298985</t>
+          <t>6301006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>13335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>47354</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>41176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72513</t>
+          <t>72936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403308</t>
+          <t>403659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424709</t>
+          <t>423876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265788</t>
+          <t>267100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290446</t>
+          <t>290002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679152</t>
+          <t>678729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710407</t>
+          <t>710489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65295</t>
+          <t>67078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391505</t>
+          <t>390408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408813</t>
+          <t>408666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291591</t>
+          <t>292245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314017</t>
+          <t>314468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691513</t>
+          <t>689730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721232</t>
+          <t>719641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37176</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>65139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57559</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90655</t>
+          <t>91171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564364</t>
+          <t>564276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>592239</t>
+          <t>593991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226497</t>
+          <t>227479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245663</t>
+          <t>245336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798889</t>
+          <t>798373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>831985</t>
+          <t>832779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58632</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64994</t>
+          <t>66201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100463</t>
+          <t>101557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130800</t>
+          <t>130565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182425</t>
+          <t>178931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1065988</t>
+          <t>1067922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1100377</t>
+          <t>1100832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666194</t>
+          <t>665100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>701663</t>
+          <t>700456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1743242</t>
+          <t>1746736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1794867</t>
+          <t>1795102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26334</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63729</t>
+          <t>63089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97547</t>
+          <t>97855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97394</t>
+          <t>96996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142826</t>
+          <t>141710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458231</t>
+          <t>460373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484262</t>
+          <t>483424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>663975</t>
+          <t>663667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697793</t>
+          <t>698433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129292</t>
+          <t>1130408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1174724</t>
+          <t>1175122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>69165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104384</t>
+          <t>104491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75221</t>
+          <t>73886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112471</t>
+          <t>112304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250133</t>
+          <t>250369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260970</t>
+          <t>260969</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004967</t>
+          <t>1004860</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1040473</t>
+          <t>1040186</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261715</t>
+          <t>1261882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1298965</t>
+          <t>1300300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177766</t>
+          <t>179642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234085</t>
+          <t>239247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>303343</t>
+          <t>299161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>373186</t>
+          <t>372945</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,47 +5476,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>542981</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>502007</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>595394</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>8,54%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>542981</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>499601</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>592751</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3185777</t>
+          <t>3180615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3242096</t>
+          <t>3240220</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3176939</t>
+          <t>3177180</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3246782</t>
+          <t>3250964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,42 +5594,42 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6427007</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6374594</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6467981</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>91,46%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6427007</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6377237</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6470387</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38277</t>
+          <t>37680</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47453</t>
+          <t>46284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44941</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76229</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390815</t>
+          <t>391412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412163</t>
+          <t>412022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299602</t>
+          <t>300771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322930</t>
+          <t>323817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>699918</t>
+          <t>698815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731206</t>
+          <t>731778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23502</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46480</t>
+          <t>47732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>71334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344378</t>
+          <t>346536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364641</t>
+          <t>365346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325793</t>
+          <t>324541</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348771</t>
+          <t>347992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679198</t>
+          <t>678166</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709150</t>
+          <t>707439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34799</t>
+          <t>34984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62666</t>
+          <t>63657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477205</t>
+          <t>477605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499269</t>
+          <t>499569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140958</t>
+          <t>139630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157168</t>
+          <t>157454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>625370</t>
+          <t>624379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653237</t>
+          <t>653052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39868</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69830</t>
+          <t>71941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>60475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96285</t>
+          <t>95616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111857</t>
+          <t>109506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155437</t>
+          <t>153942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1079808</t>
+          <t>1077697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1109770</t>
+          <t>1107670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>729591</t>
+          <t>730260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>764070</t>
+          <t>765401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820077</t>
+          <t>1821572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1863657</t>
+          <t>1866008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34423</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>61062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>53407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87428</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>587603</t>
+          <t>588341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>607494</t>
+          <t>607638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676696</t>
+          <t>677182</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703821</t>
+          <t>704159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1271522</t>
+          <t>1271407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1303831</t>
+          <t>1305543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51244</t>
+          <t>49521</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84902</t>
+          <t>83401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58578</t>
+          <t>58273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94318</t>
+          <t>94212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270991</t>
+          <t>269982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282837</t>
+          <t>282464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>997123</t>
+          <t>998624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1030781</t>
+          <t>1032504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1274852</t>
+          <t>1274958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1310592</t>
+          <t>1310897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140190</t>
+          <t>139962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190791</t>
+          <t>188700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241709</t>
+          <t>243753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>308340</t>
+          <t>311786</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>393869</t>
+          <t>397377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>478221</t>
+          <t>482872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3194931</t>
+          <t>3197022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3245532</t>
+          <t>3245760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3223256</t>
+          <t>3219810</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3289887</t>
+          <t>3287843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6439097</t>
+          <t>6434446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6523449</t>
+          <t>6519941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44047</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>49082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>62671</t>
+          <t>69097</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48746</t>
+          <t>55528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>86305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>517874</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461165</t>
+          <t>505780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482522</t>
+          <t>527897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>415992</t>
+          <t>452058</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>405180</t>
+          <t>439329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423976</t>
+          <t>462413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>890008</t>
+          <t>969932</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874544</t>
+          <t>952724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>903933</t>
+          <t>983501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>33216</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>24799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>45039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>70507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>459745</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421121</t>
+          <t>449473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438424</t>
+          <t>467747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>353771</t>
+          <t>389927</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342978</t>
+          <t>378609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361564</t>
+          <t>398344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>849672</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>769989</t>
+          <t>835848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>795235</t>
+          <t>861316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10743</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>29550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71733</t>
+          <t>69617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>636437</t>
+          <t>434680</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614549</t>
+          <t>422049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657521</t>
+          <t>445369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151161</t>
+          <t>169145</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141316</t>
+          <t>157947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156611</t>
+          <t>176148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>787599</t>
+          <t>603824</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>763442</t>
+          <t>589492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815242</t>
+          <t>617121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46022</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78019</t>
+          <t>79528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>47536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71956</t>
+          <t>74098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>112243</t>
+          <t>122767</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>103999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136731</t>
+          <t>145554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>974797</t>
+          <t>1068864</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>956800</t>
+          <t>1052315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>988797</t>
+          <t>1083967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>925873</t>
+          <t>801422</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906138</t>
+          <t>787113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951124</t>
+          <t>813675</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1900669</t>
+          <t>1870287</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1876181</t>
+          <t>1847500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1932521</t>
+          <t>1889055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50647</t>
+          <t>57964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54206</t>
+          <t>62039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63893</t>
+          <t>74733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98923</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>435342</t>
+          <t>523864</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424399</t>
+          <t>510000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>445515</t>
+          <t>534968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>797379</t>
+          <t>783332</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>784790</t>
+          <t>768088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>809742</t>
+          <t>794687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1232720</t>
+          <t>1307196</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1215118</t>
+          <t>1286641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250148</t>
+          <t>1323358</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56087</t>
+          <t>58149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32659</t>
+          <t>36902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237624</t>
+          <t>233068</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228064</t>
+          <t>225071</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239816</t>
+          <t>235858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>720803</t>
+          <t>800390</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>705284</t>
+          <t>786132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>730015</t>
+          <t>810619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>958428</t>
+          <t>1033458</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>944812</t>
+          <t>1016568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969219</t>
+          <t>1044607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>204382</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145822</t>
+          <t>180072</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218520</t>
+          <t>234732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>210439</t>
+          <t>238396</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171054</t>
+          <t>212922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241519</t>
+          <t>266850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>397785</t>
+          <t>442777</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>341985</t>
+          <t>402717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>443982</t>
+          <t>480931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3188714</t>
+          <t>3238094</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3157540</t>
+          <t>3207744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3230238</t>
+          <t>3262404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3364979</t>
+          <t>3396274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3333899</t>
+          <t>3367820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3404364</t>
+          <t>3421748</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6553694</t>
+          <t>6634369</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6507497</t>
+          <t>6596215</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6609494</t>
+          <t>6674429</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
